--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5514-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5514-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A818DC4D-F0D2-40AD-8E02-C8E98A230CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC38DEED-B4D9-4B40-A99D-6AA66D760DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{81FC880F-6B8D-4BBA-BAAB-D9B442AB2A8E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{160845CF-5A36-4A65-919F-46492400EA48}"/>
   </bookViews>
   <sheets>
     <sheet name="5514-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,29 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174E670-3783-40CF-B186-89C54C054818}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2192B5D8-5C93-4FB9-9E87-1CA4CB29A79A}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1626,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1662,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1714,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1783,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -1999,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="42">
         <v>2020</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="44"/>
       <c r="B10" s="45"/>
       <c r="C10" s="18" t="s">
@@ -2171,7 +2170,7 @@
       <c r="W10" s="51"/>
       <c r="X10" s="47"/>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="52">
         <v>2019</v>
       </c>
@@ -2243,7 +2242,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="54"/>
       <c r="B12" s="55"/>
       <c r="C12" s="20" t="s">
@@ -2271,7 +2270,7 @@
       <c r="W12" s="61"/>
       <c r="X12" s="57"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2018</v>
       </c>
@@ -2343,7 +2342,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2017</v>
       </c>
@@ -2415,7 +2414,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2016</v>
       </c>
@@ -2487,7 +2486,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2015</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2014</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2013</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2012</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2011</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2010</v>
       </c>
@@ -2919,7 +2918,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2009</v>
       </c>
@@ -2991,7 +2990,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2008</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2007</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2006</v>
       </c>
@@ -3207,7 +3206,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2005</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2004</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2003</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2002</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2001</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2000</v>
       </c>
@@ -3639,7 +3638,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1999</v>
       </c>
@@ -3711,7 +3710,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>1998</v>
       </c>
@@ -3783,7 +3782,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="45"/>
       <c r="C34" s="18" t="s">
@@ -3811,7 +3810,7 @@
       <c r="W34" s="51"/>
       <c r="X34" s="47"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>1997</v>
       </c>
@@ -3883,7 +3882,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>1996</v>
       </c>
@@ -3955,7 +3954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>1995</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1994</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>1993</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>1992</v>
       </c>
@@ -4243,7 +4242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40" t="s">
         <v>58</v>
       </c>
